--- a/templates/eudamed_master_data_universal.xlsx
+++ b/templates/eudamed_master_data_universal.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -437,15 +437,16 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
-    <col width="25" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="25" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -481,52 +482,57 @@
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
+          <t>special_device</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
           <t>active</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>implantable</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>measuring_function</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>reusable</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>administering_medicine</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>animal_tissues_cells</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>human_tissues_cells</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>human_product_check</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>medicinal_product_check</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="12">
+  <dataValidations count="13">
     <dataValidation sqref="B2:B201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"EUDAMED,GS1,HIBCC,ICCBBA,IFA"</formula1>
     </dataValidation>
@@ -537,7 +543,7 @@
       <formula1>"DEVICE,SYSTEM,PROCEDURE_PACK"</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"TRUE,FALSE"</formula1>
+      <formula1>"MDR_SOFTWARE,MDR_STANDARD_SOFT_CONTACT_LENSES,MDR_RIGID_GAS_PERMEABLE,MDR_MADE_TO_ORDER,MDR_SPECTACLES_FRAMES,MDR_SPECTACLES_LENSES,MDR_READY_MADE_SPECTACLES,MDR_ORTHOPEDIC,MDR_MADE_TO_ORDER_RIGID_GAS_PERMEABLE,MDD_SOFTWARE,MDD_STANDARD_SOFT_CONTACT_LENSES,MDD_RIGID_GAS_PERMEABLE,MDD_MADE_TO_ORDER,MDD_SPECTACLES_FRAMES,MDD_SPECTACLES_LENSES,MDD_READY_MADE_SPECTACLES,MDD_ORTHOPEDIC,AIMDD_SOFTWARE,AIMDD_ORTHOPEDIC"</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"TRUE,FALSE"</formula1>
@@ -561,6 +567,9 @@
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
     <dataValidation sqref="O2:O201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="P2:P201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>

--- a/templates/eudamed_master_data_universal.xlsx
+++ b/templates/eudamed_master_data_universal.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -437,16 +437,17 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
     <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="25" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,57 +483,62 @@
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
+          <t>applicable_legislation</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
           <t>special_device</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>implantable</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>measuring_function</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>reusable</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>administering_medicine</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>animal_tissues_cells</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>human_tissues_cells</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>human_product_check</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>medicinal_product_check</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="13">
+  <dataValidations count="14">
     <dataValidation sqref="B2:B201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"EUDAMED,GS1,HIBCC,ICCBBA,IFA"</formula1>
     </dataValidation>
@@ -543,11 +549,11 @@
       <formula1>"DEVICE,SYSTEM,PROCEDURE_PACK"</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"MDR,MDD,AIMDD"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"MDR_SOFTWARE,MDR_STANDARD_SOFT_CONTACT_LENSES,MDR_RIGID_GAS_PERMEABLE,MDR_MADE_TO_ORDER,MDR_SPECTACLES_FRAMES,MDR_SPECTACLES_LENSES,MDR_READY_MADE_SPECTACLES,MDR_ORTHOPEDIC,MDR_MADE_TO_ORDER_RIGID_GAS_PERMEABLE,MDD_SOFTWARE,MDD_STANDARD_SOFT_CONTACT_LENSES,MDD_RIGID_GAS_PERMEABLE,MDD_MADE_TO_ORDER,MDD_SPECTACLES_FRAMES,MDD_SPECTACLES_LENSES,MDD_READY_MADE_SPECTACLES,MDD_ORTHOPEDIC,AIMDD_SOFTWARE,AIMDD_ORTHOPEDIC"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
     <dataValidation sqref="I2:I201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
@@ -570,6 +576,9 @@
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
     <dataValidation sqref="P2:P201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="Q2:Q201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
